--- a/IPC_Categoría.xlsx
+++ b/IPC_Categoría.xlsx
@@ -820,7 +820,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>0.005072919757273551</v>
+        <v>0.005072919757273552</v>
       </c>
       <c r="C2" s="2">
         <v>111.9282710626499</v>
@@ -840,7 +840,7 @@
         <v>106.1498940178463</v>
       </c>
       <c r="D3" s="2">
-        <v>0.008859973316911691</v>
+        <v>0.00885997331691169</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -854,7 +854,7 @@
         <v>117.4203143698698</v>
       </c>
       <c r="D4" s="2">
-        <v>0.002546220001030067</v>
+        <v>0.002546220001030066</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -868,7 +868,7 @@
         <v>140.9902884920846</v>
       </c>
       <c r="D5" s="2">
-        <v>0.009282095859673439</v>
+        <v>0.009282095859673437</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -921,10 +921,10 @@
         <v>0.009279354150038282</v>
       </c>
       <c r="C9" s="2">
-        <v>121.336810766649</v>
+        <v>121.3368107666489</v>
       </c>
       <c r="D9" s="2">
-        <v>0.009279354150038282</v>
+        <v>0.00927935415003828</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -938,7 +938,7 @@
         <v>118.6132825202857</v>
       </c>
       <c r="D10" s="2">
-        <v>0.0005071907989218156</v>
+        <v>0.0005071907989218155</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -952,7 +952,7 @@
         <v>123.1052954193234</v>
       </c>
       <c r="D11" s="2">
-        <v>0.00578336671593761</v>
+        <v>0.005783366715937609</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -963,7 +963,7 @@
         <v>0.03020577392675578</v>
       </c>
       <c r="C12" s="2">
-        <v>112.9547034967934</v>
+        <v>112.9547034967935</v>
       </c>
       <c r="D12" s="2">
         <v>0.03020577392675578</v>
@@ -974,13 +974,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>0.02607771248356694</v>
+        <v>0.02607771248356693</v>
       </c>
       <c r="C13" s="2">
         <v>107.5233034443648</v>
       </c>
       <c r="D13" s="2">
-        <v>0.02607771248356694</v>
+        <v>0.02607771248356693</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -994,7 +994,7 @@
         <v>111.3398130961371</v>
       </c>
       <c r="D14" s="2">
-        <v>0.01309694319486418</v>
+        <v>0.01309694319486417</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1022,7 +1022,7 @@
         <v>110.9804159068862</v>
       </c>
       <c r="D16" s="2">
-        <v>0.01359861820889632</v>
+        <v>0.01359861820889631</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1033,7 +1033,7 @@
         <v>0.01928869969330398</v>
       </c>
       <c r="C17" s="2">
-        <v>107.8980464321723</v>
+        <v>107.8980464321724</v>
       </c>
       <c r="D17" s="2">
         <v>0.01928869969330398</v>
@@ -1058,7 +1058,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="2">
-        <v>0.003865794805332887</v>
+        <v>0.003865794805332888</v>
       </c>
       <c r="C19" s="2">
         <v>110.6185748351489</v>
@@ -1072,13 +1072,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2">
-        <v>0.0007394912271096146</v>
+        <v>0.0007394912271096145</v>
       </c>
       <c r="C20" s="2">
         <v>112.7549908247973</v>
       </c>
       <c r="D20" s="2">
-        <v>0.0007394912271096146</v>
+        <v>0.0007394912271096143</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1086,13 +1086,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2">
-        <v>0.0008425152421623416</v>
+        <v>0.0008425152421623413</v>
       </c>
       <c r="C21" s="2">
         <v>147.0733031615884</v>
       </c>
       <c r="D21" s="2">
-        <v>0.0008425152421623416</v>
+        <v>0.0008425152421623411</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1106,7 +1106,7 @@
         <v>113.6655973554545</v>
       </c>
       <c r="D22" s="2">
-        <v>0.001542812596938846</v>
+        <v>0.001542812596938845</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1134,7 +1134,7 @@
         <v>121.6849944029754</v>
       </c>
       <c r="D24" s="2">
-        <v>0.002621123712812744</v>
+        <v>0.002621123712812743</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1184,7 +1184,7 @@
         <v>30</v>
       </c>
       <c r="B28" s="2">
-        <v>0.004871767549653516</v>
+        <v>0.004871767549653517</v>
       </c>
       <c r="C28" s="2">
         <v>121.444736749867</v>
@@ -1232,7 +1232,7 @@
         <v>101.2542268572998</v>
       </c>
       <c r="D31" s="2">
-        <v>0.002339898716853272</v>
+        <v>0.002339898716853271</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1260,7 +1260,7 @@
         <v>145.4023667235494</v>
       </c>
       <c r="D33" s="2">
-        <v>0.003536339811892501</v>
+        <v>0.0035363398118925</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1274,7 +1274,7 @@
         <v>134.2925884573673</v>
       </c>
       <c r="D34" s="2">
-        <v>0.004714428254932481</v>
+        <v>0.00471442825493248</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1302,7 +1302,7 @@
         <v>106.0534301652215</v>
       </c>
       <c r="D36" s="2">
-        <v>0.008235553985200924</v>
+        <v>0.008235553985200922</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1316,7 +1316,7 @@
         <v>115.3743905726049</v>
       </c>
       <c r="D37" s="2">
-        <v>0.001068703530255678</v>
+        <v>0.001068703530255677</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1324,13 +1324,13 @@
         <v>40</v>
       </c>
       <c r="B38" s="2">
-        <v>0.001677361727325672</v>
+        <v>0.001677361727325671</v>
       </c>
       <c r="C38" s="2">
         <v>114.1180631779598</v>
       </c>
       <c r="D38" s="2">
-        <v>0.001677361727325672</v>
+        <v>0.001677361727325671</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1344,7 +1344,7 @@
         <v>104.7451032421541</v>
       </c>
       <c r="D39" s="2">
-        <v>0.003033920776832152</v>
+        <v>0.003033920776832151</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1358,7 +1358,7 @@
         <v>104.1409961750541</v>
       </c>
       <c r="D40" s="2">
-        <v>0.001920698205787819</v>
+        <v>0.001920698205787818</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1366,7 +1366,7 @@
         <v>43</v>
       </c>
       <c r="B41" s="2">
-        <v>0.001829311596817195</v>
+        <v>0.001829311596817196</v>
       </c>
       <c r="C41" s="2">
         <v>125.6420830245765</v>
@@ -1386,7 +1386,7 @@
         <v>106.6623762157959</v>
       </c>
       <c r="D42" s="2">
-        <v>0.0004534060770302531</v>
+        <v>0.000453406077030253</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1414,7 +1414,7 @@
         <v>107.7493608535859</v>
       </c>
       <c r="D44" s="2">
-        <v>0.002878730579439938</v>
+        <v>0.002878730579439937</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1428,7 +1428,7 @@
         <v>139.3014956247881</v>
       </c>
       <c r="D45" s="2">
-        <v>0.002364321672286094</v>
+        <v>0.002364321672286093</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1450,7 +1450,7 @@
         <v>49</v>
       </c>
       <c r="B47" s="2">
-        <v>0.001122218697205914</v>
+        <v>0.001122218697205915</v>
       </c>
       <c r="C47" s="2">
         <v>129.0018921199543</v>
@@ -1470,7 +1470,7 @@
         <v>125.5916111746146</v>
       </c>
       <c r="D48" s="2">
-        <v>0.001465842911871496</v>
+        <v>0.001465842911871495</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1478,13 +1478,13 @@
         <v>51</v>
       </c>
       <c r="B49" s="2">
-        <v>0.003552437559175313</v>
+        <v>0.003552437559175312</v>
       </c>
       <c r="C49" s="2">
         <v>114.9766663232567</v>
       </c>
       <c r="D49" s="2">
-        <v>0.003552437559175313</v>
+        <v>0.003552437559175311</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1526,7 +1526,7 @@
         <v>129.8922997094498</v>
       </c>
       <c r="D52" s="2">
-        <v>0.002582974876055803</v>
+        <v>0.002582974876055802</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1548,7 +1548,7 @@
         <v>56</v>
       </c>
       <c r="B54" s="2">
-        <v>0.003722325944605071</v>
+        <v>0.003722325944605072</v>
       </c>
       <c r="C54" s="2">
         <v>103.2369389449865</v>
@@ -1568,7 +1568,7 @@
         <v>134.1420093196151</v>
       </c>
       <c r="D55" s="2">
-        <v>0.02093543796076694</v>
+        <v>0.02093543796076693</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1582,7 +1582,7 @@
         <v>117.0935057238577</v>
       </c>
       <c r="D56" s="2">
-        <v>0.002394938600945777</v>
+        <v>0.002394938600945776</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1590,13 +1590,13 @@
         <v>59</v>
       </c>
       <c r="B57" s="2">
-        <v>0.01071408196939178</v>
+        <v>0.01071408196939179</v>
       </c>
       <c r="C57" s="2">
         <v>107.0490733079913</v>
       </c>
       <c r="D57" s="2">
-        <v>0.01071408196939178</v>
+        <v>0.01071408196939179</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1610,7 +1610,7 @@
         <v>117.8045668030035</v>
       </c>
       <c r="D58" s="2">
-        <v>0.002699615523884324</v>
+        <v>0.002699615523884323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1624,7 +1624,7 @@
         <v>110.6604814709728</v>
       </c>
       <c r="D59" s="2">
-        <v>0.003400333230631696</v>
+        <v>0.003400333230631695</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1632,13 +1632,13 @@
         <v>62</v>
       </c>
       <c r="B60" s="2">
-        <v>0.0069608410950193</v>
+        <v>0.006960841095019298</v>
       </c>
       <c r="C60" s="2">
-        <v>125.8228061195793</v>
+        <v>125.8228061195794</v>
       </c>
       <c r="D60" s="2">
-        <v>0.0069608410950193</v>
+        <v>0.006960841095019296</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1652,7 +1652,7 @@
         <v>111.1516115143998</v>
       </c>
       <c r="D61" s="2">
-        <v>0.001687446731432621</v>
+        <v>0.00168744673143262</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -1674,13 +1674,13 @@
         <v>65</v>
       </c>
       <c r="B63" s="2">
-        <v>0.001324908174641191</v>
+        <v>0.00132490817464119</v>
       </c>
       <c r="C63" s="2">
         <v>107.401724883425</v>
       </c>
       <c r="D63" s="2">
-        <v>0.001324908174641191</v>
+        <v>0.00132490817464119</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -1708,7 +1708,7 @@
         <v>120.7050459353101</v>
       </c>
       <c r="D65" s="2">
-        <v>0.003658040834499999</v>
+        <v>0.003658040834499998</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -1722,7 +1722,7 @@
         <v>100.7685614543961</v>
       </c>
       <c r="D66" s="2">
-        <v>0.006703068699049618</v>
+        <v>0.006703068699049616</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -1730,13 +1730,13 @@
         <v>69</v>
       </c>
       <c r="B67" s="2">
-        <v>0.002294404390508186</v>
+        <v>0.002294404390508185</v>
       </c>
       <c r="C67" s="2">
         <v>106.5600880005262</v>
       </c>
       <c r="D67" s="2">
-        <v>0.002294404390508186</v>
+        <v>0.002294404390508185</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -1750,7 +1750,7 @@
         <v>106.555680005594</v>
       </c>
       <c r="D68" s="2">
-        <v>0.006160681671188752</v>
+        <v>0.006160681671188751</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -1764,7 +1764,7 @@
         <v>114.4720670955965</v>
       </c>
       <c r="D69" s="2">
-        <v>0.01514298426731989</v>
+        <v>0.01514298426731988</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -1772,7 +1772,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="2">
-        <v>0.007203136928336721</v>
+        <v>0.007203136928336722</v>
       </c>
       <c r="C70" s="2">
         <v>115.3664788537881</v>
@@ -1789,7 +1789,7 @@
         <v>0.01381749199465612</v>
       </c>
       <c r="C71" s="2">
-        <v>111.8584076785985</v>
+        <v>111.8584076785986</v>
       </c>
       <c r="D71" s="2">
         <v>0.01381749199465612</v>
@@ -1806,7 +1806,7 @@
         <v>106.0362070688473</v>
       </c>
       <c r="D72" s="2">
-        <v>0.00794726616415295</v>
+        <v>0.007947266164152948</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -1814,13 +1814,13 @@
         <v>75</v>
       </c>
       <c r="B73" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
       <c r="C73" s="2">
         <v>110.2608888292721</v>
       </c>
       <c r="D73" s="2">
-        <v>0.002771663492127025</v>
+        <v>0.002771663492127026</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -1834,7 +1834,7 @@
         <v>140.1677028555776</v>
       </c>
       <c r="D74" s="2">
-        <v>0.004287135021955557</v>
+        <v>0.004287135021955556</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -1848,7 +1848,7 @@
         <v>130.3266217145816</v>
       </c>
       <c r="D75" s="2">
-        <v>0.002239187229884928</v>
+        <v>0.002239187229884927</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -1862,7 +1862,7 @@
         <v>122.5725893240119</v>
       </c>
       <c r="D76" s="2">
-        <v>0.0005641748576908801</v>
+        <v>0.00056417485769088</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -1870,13 +1870,13 @@
         <v>79</v>
       </c>
       <c r="B77" s="2">
-        <v>0.003340150088683029</v>
+        <v>0.003340150088683028</v>
       </c>
       <c r="C77" s="2">
         <v>124.9914840788052</v>
       </c>
       <c r="D77" s="2">
-        <v>0.003340150088683029</v>
+        <v>0.003340150088683028</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -1890,7 +1890,7 @@
         <v>103.4747290871829</v>
       </c>
       <c r="D78" s="2">
-        <v>0.003761360513208909</v>
+        <v>0.003761360513208908</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -1898,13 +1898,13 @@
         <v>81</v>
       </c>
       <c r="B79" s="2">
-        <v>0.003740799964779363</v>
+        <v>0.003740799964779362</v>
       </c>
       <c r="C79" s="2">
         <v>102.251517095731</v>
       </c>
       <c r="D79" s="2">
-        <v>0.003740799964779363</v>
+        <v>0.003740799964779361</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -1932,7 +1932,7 @@
         <v>106.1163653550094</v>
       </c>
       <c r="D81" s="2">
-        <v>0.005847275376675335</v>
+        <v>0.005847275376675334</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -1946,7 +1946,7 @@
         <v>100.7715822658189</v>
       </c>
       <c r="D82" s="2">
-        <v>0.005711890493465143</v>
+        <v>0.005711890493465142</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -1954,7 +1954,7 @@
         <v>85</v>
       </c>
       <c r="B83" s="2">
-        <v>0.00792684082571349</v>
+        <v>0.007926840825713492</v>
       </c>
       <c r="C83" s="2">
         <v>102.2890565867661</v>
@@ -1968,13 +1968,13 @@
         <v>86</v>
       </c>
       <c r="B84" s="2">
-        <v>0.007471334463825881</v>
+        <v>0.007471334463825879</v>
       </c>
       <c r="C84" s="2">
         <v>104.2948953686072</v>
       </c>
       <c r="D84" s="2">
-        <v>0.007471334463825881</v>
+        <v>0.007471334463825877</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2002,7 +2002,7 @@
         <v>104.2979488676808</v>
       </c>
       <c r="D86" s="2">
-        <v>0.00322044276281059</v>
+        <v>0.003220442762810589</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2016,7 +2016,7 @@
         <v>104.6241275631374</v>
       </c>
       <c r="D87" s="2">
-        <v>0.004720451181454748</v>
+        <v>0.004720451181454747</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2058,7 +2058,7 @@
         <v>101.4577216846236</v>
       </c>
       <c r="D90" s="2">
-        <v>0.00312382572265998</v>
+        <v>0.003123825722659979</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2080,7 +2080,7 @@
         <v>94</v>
       </c>
       <c r="B92" s="2">
-        <v>0.002034092186191903</v>
+        <v>0.002034092186191904</v>
       </c>
       <c r="C92" s="2">
         <v>135.5285381220679</v>
@@ -2100,7 +2100,7 @@
         <v>105.8071323082324</v>
       </c>
       <c r="D93" s="2">
-        <v>0.02534236687227569</v>
+        <v>0.02534236687227568</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2108,7 +2108,7 @@
         <v>96</v>
       </c>
       <c r="B94" s="2">
-        <v>0.06465120339979126</v>
+        <v>0.06465120339979127</v>
       </c>
       <c r="C94" s="2">
         <v>111.713682362674</v>
@@ -2142,7 +2142,7 @@
         <v>107.8254204258533</v>
       </c>
       <c r="D96" s="2">
-        <v>0.006669104750236398</v>
+        <v>0.006669104750236396</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2153,7 +2153,7 @@
         <v>0.01218966429931257</v>
       </c>
       <c r="C97" s="2">
-        <v>112.9955052450362</v>
+        <v>112.9955052450361</v>
       </c>
       <c r="D97" s="2">
         <v>0.01218966429931257</v>
@@ -2178,13 +2178,13 @@
         <v>101</v>
       </c>
       <c r="B99" s="2">
-        <v>0.006406330918587829</v>
+        <v>0.006406330918587828</v>
       </c>
       <c r="C99" s="2">
         <v>124.1447056278176</v>
       </c>
       <c r="D99" s="2">
-        <v>0.006406330918587829</v>
+        <v>0.006406330918587826</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2206,13 +2206,13 @@
         <v>103</v>
       </c>
       <c r="B101" s="2">
-        <v>0.01984503538401583</v>
+        <v>0.01984503538401582</v>
       </c>
       <c r="C101" s="2">
-        <v>106.1586938021528</v>
+        <v>106.1586938021527</v>
       </c>
       <c r="D101" s="2">
-        <v>0.01984503538401583</v>
+        <v>0.01984503538401582</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2223,7 +2223,7 @@
         <v>0.01026379595995948</v>
       </c>
       <c r="C102" s="2">
-        <v>116.3331782267851</v>
+        <v>116.3331782267852</v>
       </c>
       <c r="D102" s="2">
         <v>0.01026379595995948</v>
@@ -2234,10 +2234,10 @@
         <v>105</v>
       </c>
       <c r="B103" s="2">
-        <v>0.007749148682337151</v>
+        <v>0.007749148682337153</v>
       </c>
       <c r="C103" s="2">
-        <v>111.2763649678526</v>
+        <v>111.2763649678527</v>
       </c>
       <c r="D103" s="2">
         <v>0.007749148682337151</v>
@@ -2254,7 +2254,7 @@
         <v>104.1162443810259</v>
       </c>
       <c r="D104" s="2">
-        <v>0.002092316115213713</v>
+        <v>0.002092316115213712</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2262,13 +2262,13 @@
         <v>107</v>
       </c>
       <c r="B105" s="2">
-        <v>0.004501159334994294</v>
+        <v>0.004501159334994293</v>
       </c>
       <c r="C105" s="2">
         <v>108.4652647493191</v>
       </c>
       <c r="D105" s="2">
-        <v>0.004501159334994294</v>
+        <v>0.004501159334994292</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2276,13 +2276,13 @@
         <v>108</v>
       </c>
       <c r="B106" s="2">
-        <v>0.002976271920634676</v>
+        <v>0.002976271920634675</v>
       </c>
       <c r="C106" s="2">
         <v>117.3352509416753</v>
       </c>
       <c r="D106" s="2">
-        <v>0.002976271920634676</v>
+        <v>0.002976271920634674</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2304,7 +2304,7 @@
         <v>110</v>
       </c>
       <c r="B108" s="2">
-        <v>0.005697231293520731</v>
+        <v>0.005697231293520732</v>
       </c>
       <c r="C108" s="2">
         <v>118.4440206437201</v>
@@ -2318,13 +2318,13 @@
         <v>111</v>
       </c>
       <c r="B109" s="2">
-        <v>0.003897798195780221</v>
+        <v>0.00389779819578022</v>
       </c>
       <c r="C109" s="2">
         <v>100.8199980162666</v>
       </c>
       <c r="D109" s="2">
-        <v>0.003897798195780221</v>
+        <v>0.003897798195780219</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2332,13 +2332,13 @@
         <v>112</v>
       </c>
       <c r="B110" s="2">
-        <v>0.002520586117202039</v>
+        <v>0.002520586117202038</v>
       </c>
       <c r="C110" s="2">
         <v>109.8211612559688</v>
       </c>
       <c r="D110" s="2">
-        <v>0.002520586117202039</v>
+        <v>0.002520586117202038</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2352,7 +2352,7 @@
         <v>114.8908903922698</v>
       </c>
       <c r="D111" s="2">
-        <v>0.003876239697695964</v>
+        <v>0.003876239697695963</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2366,7 +2366,7 @@
         <v>116.0636847723118</v>
       </c>
       <c r="D112" s="2">
-        <v>0.003265253531710846</v>
+        <v>0.003265253531710845</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2374,7 +2374,7 @@
         <v>115</v>
       </c>
       <c r="B113" s="2">
-        <v>0.005640666773651918</v>
+        <v>0.005640666773651919</v>
       </c>
       <c r="C113" s="2">
         <v>113.2392440696313</v>
@@ -2402,13 +2402,13 @@
         <v>117</v>
       </c>
       <c r="B115" s="2">
-        <v>0.005134180586382132</v>
+        <v>0.00513418058638213</v>
       </c>
       <c r="C115" s="2">
         <v>123.4413203762682</v>
       </c>
       <c r="D115" s="2">
-        <v>0.005134180586382132</v>
+        <v>0.005134180586382129</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2422,7 +2422,7 @@
         <v>120.0345653810588</v>
       </c>
       <c r="D116" s="2">
-        <v>0.004618478267239092</v>
+        <v>0.004618478267239091</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2430,13 +2430,13 @@
         <v>119</v>
       </c>
       <c r="B117" s="2">
-        <v>0.002057576947323736</v>
+        <v>0.002057576947323735</v>
       </c>
       <c r="C117" s="2">
         <v>101.8221212005676</v>
       </c>
       <c r="D117" s="2">
-        <v>0.002057576947323736</v>
+        <v>0.002057576947323735</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2450,7 +2450,7 @@
         <v>102.3870666822451</v>
       </c>
       <c r="D118" s="2">
-        <v>0.0004626212865031777</v>
+        <v>0.0004626212865031775</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2475,7 +2475,7 @@
         <v>0.02068809905373154</v>
       </c>
       <c r="C120" s="2">
-        <v>120.2500321345765</v>
+        <v>120.2500321345766</v>
       </c>
       <c r="D120" s="2">
         <v>0.02068809905373154</v>
@@ -2486,13 +2486,13 @@
         <v>123</v>
       </c>
       <c r="B121" s="2">
-        <v>0.004155271121448923</v>
+        <v>0.004155271121448922</v>
       </c>
       <c r="C121" s="2">
-        <v>124.4715241096653</v>
+        <v>124.4715241096654</v>
       </c>
       <c r="D121" s="2">
-        <v>0.004155271121448923</v>
+        <v>0.004155271121448922</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2514,7 +2514,7 @@
         <v>125</v>
       </c>
       <c r="B123" s="2">
-        <v>0.02503436143097277</v>
+        <v>0.02503436143097278</v>
       </c>
       <c r="C123" s="2">
         <v>137.4884033331384</v>
@@ -2531,10 +2531,10 @@
         <v>0.0555262393868587</v>
       </c>
       <c r="C124" s="2">
-        <v>118.4814175346143</v>
+        <v>118.4814175346144</v>
       </c>
       <c r="D124" s="2">
-        <v>0.0555262393868587</v>
+        <v>0.05552623938685869</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2548,7 +2548,7 @@
         <v>114.4195335301515</v>
       </c>
       <c r="D125" s="2">
-        <v>0.07006986035922064</v>
+        <v>0.07006986035922062</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2562,7 +2562,7 @@
         <v>120.347260246615</v>
       </c>
       <c r="D126" s="2">
-        <v>0.006218568967238967</v>
+        <v>0.006218568967238965</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2576,7 +2576,7 @@
         <v>113.8369996969351</v>
       </c>
       <c r="D127" s="2">
-        <v>0.005172911408333307</v>
+        <v>0.005172911408333306</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2590,7 +2590,7 @@
         <v>147.6169305330523</v>
       </c>
       <c r="D128" s="2">
-        <v>0.001501360195453038</v>
+        <v>0.001501360195453037</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2604,7 +2604,7 @@
         <v>114.8111630989187</v>
       </c>
       <c r="D129" s="2">
-        <v>0.01581894683757622</v>
+        <v>0.01581894683757621</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2612,7 +2612,7 @@
         <v>132</v>
       </c>
       <c r="B130" s="2">
-        <v>0.003063062324578662</v>
+        <v>0.003063062324578663</v>
       </c>
       <c r="C130" s="2">
         <v>103.3156397339718</v>
@@ -2626,13 +2626,13 @@
         <v>133</v>
       </c>
       <c r="B131" s="2">
-        <v>0.01283849732236524</v>
+        <v>0.01283849732236523</v>
       </c>
       <c r="C131" s="2">
         <v>101.0725826868128</v>
       </c>
       <c r="D131" s="2">
-        <v>0.01283849732236524</v>
+        <v>0.01283849732236523</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2674,7 +2674,7 @@
         <v>100.2049998752557</v>
       </c>
       <c r="D134" s="2">
-        <v>0.002612091938062684</v>
+        <v>0.002612091938062683</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -2682,7 +2682,7 @@
         <v>137</v>
       </c>
       <c r="B135" s="2">
-        <v>0.009019747805244652</v>
+        <v>0.009019747805244654</v>
       </c>
       <c r="C135" s="2">
         <v>100.7946790929326</v>
@@ -2710,13 +2710,13 @@
         <v>139</v>
       </c>
       <c r="B137" s="2">
-        <v>0.004256005670837606</v>
+        <v>0.004256005670837605</v>
       </c>
       <c r="C137" s="2">
         <v>133.3100240041985</v>
       </c>
       <c r="D137" s="2">
-        <v>0.004256005670837606</v>
+        <v>0.004256005670837604</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -2738,10 +2738,10 @@
         <v>141</v>
       </c>
       <c r="B139" s="2">
-        <v>0.009940756973402774</v>
+        <v>0.009940756973402775</v>
       </c>
       <c r="C139" s="2">
-        <v>100.4446982414779</v>
+        <v>100.4446982414778</v>
       </c>
       <c r="D139" s="2">
         <v>0.009940756973402774</v>
